--- a/data/기초자료_4차.xlsx
+++ b/data/기초자료_4차.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\5.배관투자\2026년_2차\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\5.배관투자\2026년_4차\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0475DBFA-EFE2-4698-99F4-B843D7717BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC22103-6206-4986-A844-A08B155898AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{E01E8F30-5356-452D-9A9C-6D4CC24C1008}"/>
+    <workbookView xWindow="-28920" yWindow="585" windowWidth="29040" windowHeight="15720" xr2:uid="{DE8D305A-5348-4651-9F8A-942D9DE7BB95}"/>
   </bookViews>
   <sheets>
     <sheet name="raw (2)" sheetId="2" r:id="rId1"/>
@@ -255,22 +255,22 @@
     <t>수요조사후분석</t>
   </si>
   <si>
-    <t>노원동 대구그린스타트업타운 인입</t>
+    <t>현풍읍 중리 123번지(K구간)</t>
+  </si>
+  <si>
+    <t>비산동 698-55번지 (K구간)</t>
+  </si>
+  <si>
+    <t>원효로 24-2번지(K구간)</t>
+  </si>
+  <si>
+    <t>노원동 대구그린스타트업타운 인입2</t>
   </si>
   <si>
     <t>2026-2C00011</t>
   </si>
   <si>
     <t>기본설계후</t>
-  </si>
-  <si>
-    <t>현풍읍 중리 123번지(K구간)</t>
-  </si>
-  <si>
-    <t>비산동 698-55번지 (K구간)</t>
-  </si>
-  <si>
-    <t>원효로 24-2번지(K구간)</t>
   </si>
   <si>
     <t>용도</t>
@@ -383,7 +383,7 @@
     <t>주택용인입관비배분액</t>
   </si>
   <si>
-    <t>노원동대구그린스타트업타운인입</t>
+    <t>노원동대구그린스타트업타운인입2</t>
   </si>
 </sst>
 </file>
@@ -1025,8 +1025,8 @@
     <cellStyle name="보통" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="설명 텍스트" xfId="16" builtinId="53" customBuiltin="1"/>
     <cellStyle name="셀 확인" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="쉼표 [0] 2" xfId="43" xr:uid="{179B5581-0CB3-4581-9069-0CC4584666A7}"/>
-    <cellStyle name="쉼표 [0] 3" xfId="42" xr:uid="{A9EF6240-B77A-4012-B0CF-CD5B64A766DD}"/>
+    <cellStyle name="쉼표 [0] 2" xfId="43" xr:uid="{BD8A31C1-8260-433D-B0D8-BD63AEE0A4E8}"/>
+    <cellStyle name="쉼표 [0] 3" xfId="42" xr:uid="{57839252-6185-4F44-91C2-45905D7FB614}"/>
     <cellStyle name="연결된 셀" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="요약" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="입력" xfId="9" builtinId="20" customBuiltin="1"/>
@@ -1368,13 +1368,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{525AF2BC-A85C-496B-AA8F-BFA67F28412C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8263BAB-AE75-43D9-BB34-025E18A23CA1}">
   <dimension ref="A1:BS5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="23.5" customWidth="1"/>
-    <col min="5" max="5" width="15.625" customWidth="1"/>
-    <col min="7" max="7" width="13.625" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="7" max="7" width="12.5" customWidth="1"/>
+    <col min="64" max="68" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:71" x14ac:dyDescent="0.3">
@@ -1676,16 +1676,16 @@
         <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F5">
         <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>21127000</v>
+        <v>19077000</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1865,13 +1865,13 @@
         <v>3145341</v>
       </c>
       <c r="BO5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BP5" s="1">
-        <v>14279550</v>
+        <v>16125898</v>
       </c>
       <c r="BQ5">
-        <v>12.46</v>
+        <v>14</v>
       </c>
       <c r="BR5">
         <v>285.7</v>
@@ -1887,12 +1887,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61F0EF06-0D40-4D2D-B889-718599A0758C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15EEEB14-E1A6-4BD7-B7ED-E8039919D473}">
   <dimension ref="A1:BR10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20.25" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -2390,19 +2387,13 @@
         <v>73</v>
       </c>
       <c r="B6">
-        <v>10011500</v>
-      </c>
-      <c r="C6" t="s">
-        <v>74</v>
+        <v>10011501</v>
       </c>
       <c r="D6" t="s">
         <v>72</v>
       </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
       <c r="F6" s="1">
-        <v>20000000</v>
+        <v>11286000</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2414,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -2447,13 +2438,13 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>2</v>
-      </c>
-      <c r="V6" s="1">
-        <v>39600</v>
-      </c>
-      <c r="W6" s="1">
-        <v>49501</v>
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
       </c>
       <c r="X6">
         <v>0</v>
@@ -2486,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI6">
         <v>0</v>
@@ -2501,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AN6">
         <v>0</v>
@@ -2516,19 +2507,19 @@
         <v>0</v>
       </c>
       <c r="AR6">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="AS6" s="1">
-        <v>1818400</v>
+        <v>181840</v>
       </c>
       <c r="AT6">
         <v>0</v>
       </c>
-      <c r="AU6">
-        <v>0</v>
+      <c r="AU6" s="1">
+        <v>2355672</v>
       </c>
       <c r="AV6" s="1">
-        <v>1818400</v>
+        <v>2537512</v>
       </c>
       <c r="AW6">
         <v>0</v>
@@ -2536,8 +2527,8 @@
       <c r="AX6">
         <v>0</v>
       </c>
-      <c r="AY6">
-        <v>0</v>
+      <c r="AY6" s="1">
+        <v>55752</v>
       </c>
       <c r="AZ6">
         <v>0</v>
@@ -2551,11 +2542,11 @@
       <c r="BC6">
         <v>0</v>
       </c>
-      <c r="BD6" s="1">
-        <v>475211</v>
-      </c>
-      <c r="BE6" s="1">
-        <v>594014</v>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
       </c>
       <c r="BF6">
         <v>0</v>
@@ -2570,28 +2561,28 @@
         <v>0</v>
       </c>
       <c r="BJ6" s="1">
-        <v>1069225</v>
+        <v>55752</v>
       </c>
       <c r="BK6" s="1">
-        <v>18278399</v>
+        <v>1317758</v>
       </c>
       <c r="BL6" s="1">
-        <v>15133058</v>
+        <v>1162400</v>
       </c>
       <c r="BM6" s="1">
-        <v>3145341</v>
+        <v>155358</v>
       </c>
       <c r="BN6">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="BO6" s="1">
-        <v>15294591</v>
+        <v>4276108</v>
       </c>
       <c r="BP6">
-        <v>13.27</v>
+        <v>-4.6500000000000004</v>
       </c>
       <c r="BQ6">
-        <v>285.7</v>
+        <v>7.4</v>
       </c>
       <c r="BR6">
         <v>0</v>
@@ -2599,22 +2590,16 @@
     </row>
     <row r="7" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7">
-        <v>10011500</v>
-      </c>
-      <c r="C7" t="s">
-        <v>74</v>
+        <v>10011502</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="F7" s="1">
-        <v>21127000</v>
+        <v>4180000</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2626,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -2659,13 +2644,13 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>2</v>
-      </c>
-      <c r="V7" s="1">
-        <v>39600</v>
-      </c>
-      <c r="W7" s="1">
-        <v>49501</v>
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
       </c>
       <c r="X7">
         <v>0</v>
@@ -2698,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI7">
         <v>0</v>
@@ -2713,7 +2698,7 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AN7">
         <v>0</v>
@@ -2728,19 +2713,19 @@
         <v>0</v>
       </c>
       <c r="AR7">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="AS7" s="1">
-        <v>1818400</v>
+        <v>181840</v>
       </c>
       <c r="AT7">
         <v>0</v>
       </c>
-      <c r="AU7">
-        <v>0</v>
+      <c r="AU7" s="1">
+        <v>466720</v>
       </c>
       <c r="AV7" s="1">
-        <v>1818400</v>
+        <v>648560</v>
       </c>
       <c r="AW7">
         <v>0</v>
@@ -2748,8 +2733,8 @@
       <c r="AX7">
         <v>0</v>
       </c>
-      <c r="AY7">
-        <v>0</v>
+      <c r="AY7" s="1">
+        <v>55752</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -2763,11 +2748,11 @@
       <c r="BC7">
         <v>0</v>
       </c>
-      <c r="BD7" s="1">
-        <v>475211</v>
-      </c>
-      <c r="BE7" s="1">
-        <v>594014</v>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
       </c>
       <c r="BF7">
         <v>0</v>
@@ -2782,28 +2767,28 @@
         <v>0</v>
       </c>
       <c r="BJ7" s="1">
-        <v>1069225</v>
+        <v>55752</v>
       </c>
       <c r="BK7" s="1">
-        <v>18278399</v>
+        <v>1317759</v>
       </c>
       <c r="BL7" s="1">
-        <v>15133058</v>
+        <v>1162401</v>
       </c>
       <c r="BM7" s="1">
-        <v>3145341</v>
+        <v>155358</v>
       </c>
       <c r="BN7">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="BO7" s="1">
-        <v>14279550</v>
+        <v>2387156</v>
       </c>
       <c r="BP7">
-        <v>12.46</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="BQ7">
-        <v>285.7</v>
+        <v>20</v>
       </c>
       <c r="BR7">
         <v>0</v>
@@ -2811,16 +2796,16 @@
     </row>
     <row r="8" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8">
-        <v>10011501</v>
+        <v>10011503</v>
       </c>
       <c r="D8" t="s">
         <v>72</v>
       </c>
       <c r="F8" s="1">
-        <v>11286000</v>
+        <v>6688000</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2832,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -2898,13 +2883,13 @@
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG8">
         <v>0</v>
       </c>
       <c r="AH8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AI8">
         <v>0</v>
@@ -2934,19 +2919,19 @@
         <v>0</v>
       </c>
       <c r="AR8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AS8" s="1">
-        <v>181840</v>
+        <v>90920</v>
       </c>
       <c r="AT8">
         <v>0</v>
       </c>
       <c r="AU8" s="1">
-        <v>2355672</v>
+        <v>1455624</v>
       </c>
       <c r="AV8" s="1">
-        <v>2537512</v>
+        <v>1546544</v>
       </c>
       <c r="AW8">
         <v>0</v>
@@ -2955,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="AY8" s="1">
-        <v>55752</v>
+        <v>27876</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -2988,28 +2973,28 @@
         <v>0</v>
       </c>
       <c r="BJ8" s="1">
-        <v>55752</v>
+        <v>27876</v>
       </c>
       <c r="BK8" s="1">
-        <v>1317758</v>
+        <v>658879</v>
       </c>
       <c r="BL8" s="1">
-        <v>1162400</v>
+        <v>581200</v>
       </c>
       <c r="BM8" s="1">
-        <v>155358</v>
+        <v>77679</v>
       </c>
       <c r="BN8">
         <v>1</v>
       </c>
       <c r="BO8" s="1">
-        <v>4276108</v>
+        <v>2415835</v>
       </c>
       <c r="BP8">
-        <v>-4.6500000000000004</v>
+        <v>-5.44</v>
       </c>
       <c r="BQ8">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="BR8">
         <v>0</v>
@@ -3017,16 +3002,22 @@
     </row>
     <row r="9" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9">
+        <v>10011504</v>
+      </c>
+      <c r="C9" t="s">
         <v>77</v>
-      </c>
-      <c r="B9">
-        <v>10011502</v>
       </c>
       <c r="D9" t="s">
         <v>72</v>
       </c>
+      <c r="E9">
+        <v>7</v>
+      </c>
       <c r="F9" s="1">
-        <v>4180000</v>
+        <v>20000000</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -3038,46 +3029,46 @@
         <v>0</v>
       </c>
       <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
         <v>2</v>
       </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
+      <c r="V9" s="1">
+        <v>39600</v>
+      </c>
+      <c r="W9" s="1">
+        <v>49501</v>
       </c>
       <c r="X9">
         <v>0</v>
@@ -3110,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="AH9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI9">
         <v>0</v>
@@ -3125,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN9">
         <v>0</v>
@@ -3140,19 +3131,19 @@
         <v>0</v>
       </c>
       <c r="AR9">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="AS9" s="1">
-        <v>181840</v>
+        <v>1818400</v>
       </c>
       <c r="AT9">
         <v>0</v>
       </c>
-      <c r="AU9" s="1">
-        <v>466720</v>
+      <c r="AU9">
+        <v>0</v>
       </c>
       <c r="AV9" s="1">
-        <v>648560</v>
+        <v>1818400</v>
       </c>
       <c r="AW9">
         <v>0</v>
@@ -3160,8 +3151,8 @@
       <c r="AX9">
         <v>0</v>
       </c>
-      <c r="AY9" s="1">
-        <v>55752</v>
+      <c r="AY9">
+        <v>0</v>
       </c>
       <c r="AZ9">
         <v>0</v>
@@ -3175,11 +3166,11 @@
       <c r="BC9">
         <v>0</v>
       </c>
-      <c r="BD9">
-        <v>0</v>
-      </c>
-      <c r="BE9">
-        <v>0</v>
+      <c r="BD9" s="1">
+        <v>475211</v>
+      </c>
+      <c r="BE9" s="1">
+        <v>594014</v>
       </c>
       <c r="BF9">
         <v>0</v>
@@ -3194,28 +3185,28 @@
         <v>0</v>
       </c>
       <c r="BJ9" s="1">
-        <v>55752</v>
+        <v>1069225</v>
       </c>
       <c r="BK9" s="1">
-        <v>1317759</v>
+        <v>18278399</v>
       </c>
       <c r="BL9" s="1">
-        <v>1162401</v>
+        <v>15133058</v>
       </c>
       <c r="BM9" s="1">
-        <v>155358</v>
+        <v>3145341</v>
       </c>
       <c r="BN9">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="BO9" s="1">
-        <v>2387156</v>
+        <v>15294591</v>
       </c>
       <c r="BP9">
-        <v>0.56999999999999995</v>
+        <v>13.27</v>
       </c>
       <c r="BQ9">
-        <v>20</v>
+        <v>285.7</v>
       </c>
       <c r="BR9">
         <v>0</v>
@@ -3223,16 +3214,22 @@
     </row>
     <row r="10" spans="1:70" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10">
+        <v>10011504</v>
+      </c>
+      <c r="C10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" t="s">
         <v>78</v>
       </c>
-      <c r="B10">
-        <v>10011503</v>
-      </c>
-      <c r="D10" t="s">
-        <v>72</v>
+      <c r="E10">
+        <v>7</v>
       </c>
       <c r="F10" s="1">
-        <v>6688000</v>
+        <v>19077000</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -3244,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3277,13 +3274,13 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="V10" s="1">
+        <v>39600</v>
+      </c>
+      <c r="W10" s="1">
+        <v>49501</v>
       </c>
       <c r="X10">
         <v>0</v>
@@ -3310,13 +3307,13 @@
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG10">
         <v>0</v>
       </c>
       <c r="AH10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI10">
         <v>0</v>
@@ -3331,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN10">
         <v>0</v>
@@ -3346,19 +3343,19 @@
         <v>0</v>
       </c>
       <c r="AR10">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="AS10" s="1">
-        <v>90920</v>
+        <v>1818400</v>
       </c>
       <c r="AT10">
         <v>0</v>
       </c>
-      <c r="AU10" s="1">
-        <v>1455624</v>
+      <c r="AU10">
+        <v>0</v>
       </c>
       <c r="AV10" s="1">
-        <v>1546544</v>
+        <v>1818400</v>
       </c>
       <c r="AW10">
         <v>0</v>
@@ -3366,8 +3363,8 @@
       <c r="AX10">
         <v>0</v>
       </c>
-      <c r="AY10" s="1">
-        <v>27876</v>
+      <c r="AY10">
+        <v>0</v>
       </c>
       <c r="AZ10">
         <v>0</v>
@@ -3381,11 +3378,11 @@
       <c r="BC10">
         <v>0</v>
       </c>
-      <c r="BD10">
-        <v>0</v>
-      </c>
-      <c r="BE10">
-        <v>0</v>
+      <c r="BD10" s="1">
+        <v>475211</v>
+      </c>
+      <c r="BE10" s="1">
+        <v>594014</v>
       </c>
       <c r="BF10">
         <v>0</v>
@@ -3400,28 +3397,28 @@
         <v>0</v>
       </c>
       <c r="BJ10" s="1">
-        <v>27876</v>
+        <v>1069225</v>
       </c>
       <c r="BK10" s="1">
-        <v>658879</v>
+        <v>18278399</v>
       </c>
       <c r="BL10" s="1">
-        <v>581200</v>
+        <v>15133058</v>
       </c>
       <c r="BM10" s="1">
-        <v>77679</v>
+        <v>3145341</v>
       </c>
       <c r="BN10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="BO10" s="1">
-        <v>2415835</v>
+        <v>16125898</v>
       </c>
       <c r="BP10">
-        <v>-5.44</v>
+        <v>14</v>
       </c>
       <c r="BQ10">
-        <v>6.3</v>
+        <v>285.7</v>
       </c>
       <c r="BR10">
         <v>0</v>
